--- a/Deaths_due_to_dementia_2023_tidy.xlsx
+++ b/Deaths_due_to_dementia_2023_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\OneDrive\Desktop\health-data-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{267B07F3-4B42-4699-8AEE-2DB53F457F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{335A88BD-0489-4F8E-8397-4E62B6A812BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FCF7FC-8A51-403A-9B2F-8B13C6C6C3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B7C280E-A26D-4087-85B3-71D7CD546D7A}"/>
+    <workbookView xWindow="1644" yWindow="1980" windowWidth="17280" windowHeight="8880" xr2:uid="{7B7C280E-A26D-4087-85B3-71D7CD546D7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>0–59</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Females</t>
+  </si>
+  <si>
+    <t>Males_rate</t>
+  </si>
+  <si>
+    <t>Females_rate</t>
   </si>
 </sst>
 </file>
@@ -433,13 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF651CA0-3C31-476C-A956-49B9EBB5C6C6}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -449,8 +455,14 @@
       <c r="C1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -460,8 +472,14 @@
       <c r="C2" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="1">
+        <v>0.25086829375982489</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.20566166990420573</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -471,8 +489,14 @@
       <c r="C3" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="1">
+        <v>5.2811322747597087</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6.2877505636519251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -482,8 +506,14 @@
       <c r="C4" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="1">
+        <v>17.712431619041649</v>
+      </c>
+      <c r="E4" s="1">
+        <v>17.381882863491384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -493,8 +523,14 @@
       <c r="C5" s="1">
         <v>366</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="1">
+        <v>61.311857352554</v>
+      </c>
+      <c r="E5" s="1">
+        <v>60.69279331118986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -504,8 +540,14 @@
       <c r="C6" s="1">
         <v>926</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="1">
+        <v>180.74656188605107</v>
+      </c>
+      <c r="E6" s="1">
+        <v>191.05743896375066</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -515,8 +557,14 @@
       <c r="C7" s="1">
         <v>1667</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <v>497.54203821182352</v>
+      </c>
+      <c r="E7" s="1">
+        <v>530.69228761166187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -526,8 +574,14 @@
       <c r="C8" s="1">
         <v>2626</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="1">
+        <v>1186.2243165799803</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1319.7903212025874</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -537,8 +591,14 @@
       <c r="C9" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="1">
+        <v>2433.191051171752</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2952.9012254540085</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -547,6 +607,12 @@
       </c>
       <c r="C10" s="3">
         <v>2115</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4084.4714213454731</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5688.0832638571392</v>
       </c>
     </row>
   </sheetData>
